--- a/lab/lab-07.xlsx
+++ b/lab/lab-07.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 Binomial Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✏️ Q1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✏️ Q2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✏️ Q3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,17 +51,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <i val="1"/>
@@ -67,14 +62,15 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Consolas"/>
+      <color rgb="001F3864"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +95,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF59D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -182,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -197,14 +203,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -213,18 +219,28 @@
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,10 +249,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,18 +261,18 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,346 +638,705 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>LAB 7 · BINOMIAL DISTRIBUTION — Excel Exercise Guide</t>
+          <t>LAB 7 · BINOMIAL DISTRIBUTION — Demonstration (we solve this one together)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Read this sheet first. Then solve Q1 to Q3 with BINOM.DIST. Data are illustrative.</t>
+          <t>Watch each step, then click a green Result cell to see the formula. Solve Q1–Q3 the same way. Data are illustrative.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IS IT BINOMIAL? ALL FOUR MUST BE TRUE</t>
+          <t>1 · IS IT BINOMIAL? ALL FOUR MUST BE TRUE</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1. A fixed number of trials, n</t>
+          <t>1.  Fixed number of trials n</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2. Each trial has two outcomes: success or failure</t>
+          <t>2.  Two outcomes: success or failure</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>3. The same probability of success p in every trial</t>
+          <t>3.  Same p in every trial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>4. The trials are independent</t>
+          <t>4.  Trials are independent</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>THE FORMULA</t>
+          <t>2 · THE FORMULAS</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>P(X = x) = nCx · pˣ · q⁽ⁿ⁻ˣ⁾</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>→  n = number of trials</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>→  x = number of successes you want</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>→  p = probability of success in one trial</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>→  q = 1 − p (probability of failure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>→  Mean μ = n·p      Var σ² = n·p·q      SD σ = √(n·p·q)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>EXCEL SYNTAX</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>=BINOM.DIST( x , n , p , FALSE or TRUE )</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>→  FALSE = exact probability ("exactly x")</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>→  TRUE = cumulative probability ("x or fewer")</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>→  nCx in Excel: =COMBIN(n, x)        powers: =0.4^3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>WHICH FORMULA DO I USE?</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>If the problem says…</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Use this formula</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>"Exactly x"</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>=BINOM.DIST(x, n, p, FALSE)</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>"At most x" / "x or fewer"</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>=BINOM.DIST(x, n, p, TRUE)</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>TRUE directly</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>"Fewer than x"</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>=BINOM.DIST(x − 1, n, p, TRUE)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>x minus 1</t>
-        </is>
-      </c>
-    </row>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Excel formula</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Exactly x</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>P(X = x) = nCx · pˣ · qⁿ⁻ˣ</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>BINOM.DIST(x, n, p, FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>At most x</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>P(X ≤ x)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>BINOM.DIST(x, n, p, TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Fewer than x</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>P(X ≤ x − 1)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>BINOM.DIST(x − 1, n, p, TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>At least x</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X ≤ x − 1)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>1 − BINOM.DIST(x − 1, n, p, TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>More than x</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X ≤ x)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>1 − BINOM.DIST(x, n, p, TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Between a and b</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>P(X ≤ b) − P(X ≤ a − 1)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>BINOM.DIST(b,…,TRUE) − BINOM.DIST(a − 1,…,TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>At least one</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X = 0)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>1 − BINOM.DIST(0, n, p, FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Mean, Var, SD</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>μ = n·p    σ² = n·p·q    σ = √(n·p·q)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>n*p   n*p*(1−p)   SQRT(…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>✓  FALSE = exact   |   TRUE = cumulative ("x or fewer")   |   "at least / more than" → 1 minus</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>3 · DEMONSTRATION — A player scores 70% of free throws. She takes 5 shots. X = number of scores.</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Check: n = 5 fixed · score or miss · p = 0.7 every shot · shots independent → binomial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>← The formulas below click these cells, so a new n or p updates every answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>q = 1 − p</t>
+        </is>
+      </c>
+      <c r="D28" s="13">
+        <f>1-D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>"At least x"</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>=1 − BINOM.DIST(x − 1, n, p, TRUE)</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>1 minus, with x − 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>"More than x"</t>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>What we want</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Excel formula</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>=1 − BINOM.DIST(x, n, p, TRUE)</t>
+          <t>P(exactly 4)   P(X = 4)</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>1 minus, x stays</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>"Between a and b" (inclusive)</t>
+          <t>Exact → FALSE</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>=BINOM.DIST(4,$D$26,$D$27,FALSE)</t>
+        </is>
+      </c>
+      <c r="F31" s="17">
+        <f>_xlfn.BINOM.DIST(4,$D$26,$D$27,FALSE)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>About 1 chance in 3 that she scores exactly 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>=BINOM.DIST(b, n, p, TRUE) − BINOM.DIST(a − 1, n, p, TRUE)</t>
+          <t>Check step 1 with the formula</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>subtract two</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>"At least one"</t>
+          <t>nCx · pˣ · qⁿ⁻ˣ</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>=COMBIN($D$26,4)*$D$27^4*$D$28^1</t>
+        </is>
+      </c>
+      <c r="F32" s="17">
+        <f>COMBIN($D$26,4)*$D$27^4*$D$28^1</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Same answer as BINOM.DIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>=1 − BINOM.DIST(0, n, p, FALSE)</t>
+          <t>P(at most 3)   P(X ≤ 3)</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>1 minus "none"</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>✓  Key rule:  FALSE = exact   |   TRUE = cumulative   |   'at least / more than' → 1 minus</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="B37" s="12" t="inlineStr">
+          <t>"At most" → TRUE</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>=BINOM.DIST(3,$D$26,$D$27,TRUE)</t>
+        </is>
+      </c>
+      <c r="F33" s="17">
+        <f>_xlfn.BINOM.DIST(3,$D$26,$D$27,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>0, 1, 2 or 3 scores together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>P(at least 4)   P(X ≥ 4)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X ≤ 3)</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>=1-BINOM.DIST(3,$D$26,$D$27,TRUE)</t>
+        </is>
+      </c>
+      <c r="F34" s="17">
+        <f>1-_xlfn.BINOM.DIST(3,$D$26,$D$27,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Steps 3 and 4 add up to 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>P(more than 2)   P(X &gt; 2)</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X ≤ 2)</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>=1-BINOM.DIST(2,$D$26,$D$27,TRUE)</t>
+        </is>
+      </c>
+      <c r="F35" s="17">
+        <f>1-_xlfn.BINOM.DIST(2,$D$26,$D$27,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>x stays at 2 inside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>P(fewer than 2)   P(X &lt; 2)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>P(X ≤ 1)</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>=BINOM.DIST(1,$D$26,$D$27,TRUE)</t>
+        </is>
+      </c>
+      <c r="F36" s="17">
+        <f>_xlfn.BINOM.DIST(1,$D$26,$D$27,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Very unlikely for a 70% shooter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>P(between 2 and 4)   P(2 ≤ X ≤ 4)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>P(X ≤ 4) − P(X ≤ 1)</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>=BINOM.DIST(4,$D$26,$D$27,TRUE)-BINOM.DIST(1,$D$26,$D$27,TRUE)</t>
+        </is>
+      </c>
+      <c r="F37" s="17">
+        <f>_xlfn.BINOM.DIST(4,$D$26,$D$27,TRUE)-_xlfn.BINOM.DIST(1,$D$26,$D$27,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>a − 1 = 1 inside the second one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>P(at least one score)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>1 − P(X = 0)</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>=1-BINOM.DIST(0,$D$26,$D$27,FALSE)</t>
+        </is>
+      </c>
+      <c r="F38" s="17">
+        <f>1-_xlfn.BINOM.DIST(0,$D$26,$D$27,FALSE)</f>
+        <v/>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Almost certain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Mean μ</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>n·p</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>=$D$26*$D$27</t>
+        </is>
+      </c>
+      <c r="F39" s="17">
+        <f>$D$26*$D$27</f>
+        <v/>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>On average 3.5 scores in 5 shots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Var σ²</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>n·p·q</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>=$D$26*$D$27*$D$28</t>
+        </is>
+      </c>
+      <c r="F40" s="17">
+        <f>$D$26*$D$27*$D$28</f>
+        <v/>
+      </c>
+      <c r="G40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>SD σ</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>√(n·p·q)</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>=SQRT($D$26*$D$27*$D$28)</t>
+        </is>
+      </c>
+      <c r="F41" s="17">
+        <f>SQRT($D$26*$D$27*$D$28)</f>
+        <v/>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>A typical set of 5 shots is about 1 score from 3.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Save as Lab7_YourName.xlsx and upload it on Moodle. Instructor: Eng. Nadia Mek.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B2:D2"/>
+  <mergeCells count="13">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -999,18 +1374,18 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Student ID:</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n"/>
+      <c r="E4" s="19" t="n"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -1030,43 +1405,43 @@
     </row>
     <row r="7"/>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Fixed n?</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Two outcomes?</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Same p?</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Independent?</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Binomial?</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>p</t>
         </is>
@@ -1083,13 +1458,13 @@
           <t>12 customers enter a shop. Each buys something with probability 0.3, independently. X = number who buy.</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="15" t="inlineStr">
@@ -1102,13 +1477,13 @@
           <t>3 cards are drawn from a deck without replacement. X = number of hearts.</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="B11" s="15" t="inlineStr">
@@ -1121,13 +1496,13 @@
           <t>A die is rolled until a 6 appears. X = number of rolls.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
@@ -1140,13 +1515,13 @@
           <t>20 phones are taken from a large production line where 4% are faulty. X = number of faulty phones.</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="B13" s="15" t="inlineStr">
@@ -1159,17 +1534,17 @@
           <t>5 restaurants are rated from 1 to 5 stars. X = the total number of stars.</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Tip: one "No" is enough to say it is not binomial.</t>
         </is>
@@ -1218,18 +1593,18 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Student ID:</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n"/>
+      <c r="E4" s="19" t="n"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -1244,7 +1619,7 @@
       <c r="F6" s="4" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>In a large survey, 40% of university students take public transport to campus. A random sample of 8 students is chosen.</t>
         </is>
@@ -1255,7 +1630,7 @@
       <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>X = number of students in the sample who take public transport.</t>
         </is>
@@ -1279,29 +1654,29 @@
     </row>
     <row r="11"/>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Type your Excel formula here</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Hint</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Guidance</t>
         </is>
       </c>
     </row>
@@ -1317,9 +1692,9 @@
 P(X = 3)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Exact → FALSE</t>
         </is>
@@ -1337,9 +1712,9 @@
 P(X ≤ 2)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>"At most" → TRUE</t>
         </is>
@@ -1357,9 +1732,9 @@
 P(X ≥ 5)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>"At least" → 1 minus, use x − 1 inside</t>
         </is>
@@ -1377,9 +1752,9 @@
 P(X &gt; 6)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>"More than" → 1 minus, x stays</t>
         </is>
@@ -1397,9 +1772,9 @@
 P(X &lt; 4)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>"Fewer than" → x − 1 with TRUE</t>
         </is>
@@ -1417,9 +1792,9 @@
 P(2 ≤ X ≤ 4)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Between → subtract two TRUE values</t>
         </is>
@@ -1436,9 +1811,9 @@
           <t>P(at least one takes public transport)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>1 minus "none"</t>
         </is>
@@ -1455,9 +1830,9 @@
           <t>Check (a) with the formula, without BINOM.DIST.</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Use =COMBIN(n, x) and powers ^</t>
         </is>
@@ -1474,9 +1849,9 @@
           <t>Mean, Var and SD of X</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>μ = n·p    σ² = n·p·q    σ = √(n·p·q)
 Write all three in E</t>
@@ -1485,14 +1860,14 @@
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>■  YELLOW = type your Excel formula</t>
         </is>
@@ -1500,12 +1875,12 @@
       <c r="C24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>■  ORANGE = write your answer (4 decimals) or your explanation</t>
         </is>
       </c>
-      <c r="C25" s="25" t="n"/>
+      <c r="C25" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1553,18 +1928,18 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Student ID:</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n"/>
+      <c r="E4" s="19" t="n"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -1581,7 +1956,7 @@
       <c r="H6" s="4" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A courier delivers 25% of parcels late. Six parcels are sent today. X = number of late parcels (n = 6, p = 0.25).</t>
         </is>
@@ -1595,22 +1970,22 @@
     </row>
     <row r="8"/>
     <row r="9" ht="22" customHeight="1">
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>P(X = x)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>P(X ≤ x)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>x · P(x)</t>
         </is>
@@ -1625,9 +2000,9 @@
       <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>1. P(X = x): BINOM.DIST with FALSE. Click the x cell, lock n and p.</t>
@@ -1638,9 +2013,9 @@
       <c r="C11" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>2. P(X ≤ x): the same with TRUE.</t>
@@ -1651,9 +2026,9 @@
       <c r="C12" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>3. Total of P(X = x) must be 1.</t>
@@ -1664,9 +2039,9 @@
       <c r="C13" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
           <t>4. x · P(x): its Total is the mean. Compare with n·p.</t>
@@ -1677,9 +2052,9 @@
       <c r="C14" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>5. Chart: select the x and P(X = x) columns → Insert → Column chart. Add a title and axis labels.</t>
@@ -1690,42 +2065,42 @@
       <c r="C15" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="C16" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="26" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
     </row>
     <row r="18"/>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
@@ -1742,9 +2117,9 @@
           <t>Which number of late parcels is the most likely?</t>
         </is>
       </c>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="31" t="n"/>
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="35" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="B21" s="15" t="inlineStr">
@@ -1757,9 +2132,9 @@
           <t>Mean from the table (Total of x·P(x)) and n·p: do they match?</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="31" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="35" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="B22" s="15" t="inlineStr">
@@ -1772,9 +2147,9 @@
           <t>Describe the shape of your chart: symmetric, right- or left-skewed? Why?</t>
         </is>
       </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="31" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="35" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="B23" s="15" t="inlineStr">
@@ -1787,20 +2162,20 @@
           <t>P(more than 2 late) from your table, without a new BINOM.DIST.</t>
         </is>
       </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="35" t="n"/>
     </row>
     <row r="24"/>
     <row r="25">
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>■  YELLOW = type your Excel formula</t>
         </is>
@@ -1810,14 +2185,14 @@
       <c r="E26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>■  ORANGE = write your answer (4 decimals) or your explanation</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
